--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>55.32 seconds</t>
+    <t>54.02 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/21/2026, 12:38:30 PM</t>
+    <t>8/21/2026, 1:32:38 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-21T12:37:46.383Z</t>
+    <t>2026-08-21T13:31:54.115Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-21T12:37:46.531Z</t>
+    <t>2026-08-21T13:31:54.236Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-21T12:37:46.645Z</t>
+    <t>2026-08-21T13:31:54.348Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:07.874Z</t>
+    <t>2026-08-21T13:32:15.700Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:08.063Z</t>
+    <t>2026-08-21T13:32:15.968Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:08.200Z</t>
+    <t>2026-08-21T13:32:16.091Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:08.326Z</t>
+    <t>2026-08-21T13:32:16.217Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:08.569Z</t>
+    <t>2026-08-21T13:32:16.434Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:08.805Z</t>
+    <t>2026-08-21T13:32:16.652Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:09.044Z</t>
+    <t>2026-08-21T13:32:16.879Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:09.278Z</t>
+    <t>2026-08-21T13:32:17.102Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:09.519Z</t>
+    <t>2026-08-21T13:32:17.334Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:10.597Z</t>
+    <t>2026-08-21T13:32:18.529Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:11.136Z</t>
+    <t>2026-08-21T13:32:19.139Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:11.767Z</t>
+    <t>2026-08-21T13:32:19.797Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:13.050Z</t>
+    <t>2026-08-21T13:32:21.233Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:13.517Z</t>
+    <t>2026-08-21T13:32:21.650Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:13.960Z</t>
+    <t>2026-08-21T13:32:22.173Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:14.226Z</t>
+    <t>2026-08-21T13:32:22.399Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:15.680Z</t>
+    <t>2026-08-21T13:32:23.713Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:15.913Z</t>
+    <t>2026-08-21T13:32:23.912Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:16.199Z</t>
+    <t>2026-08-21T13:32:24.183Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:16.543Z</t>
+    <t>2026-08-21T13:32:24.508Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:16.884Z</t>
+    <t>2026-08-21T13:32:24.775Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:17.167Z</t>
+    <t>2026-08-21T13:32:24.995Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:18.409Z</t>
+    <t>2026-08-21T13:32:26.104Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:19.553Z</t>
+    <t>2026-08-21T13:32:27.272Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:20.638Z</t>
+    <t>2026-08-21T13:32:28.322Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:22.461Z</t>
+    <t>2026-08-21T13:32:30.112Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:24.289Z</t>
+    <t>2026-08-21T13:32:31.902Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:24.555Z</t>
+    <t>2026-08-21T13:32:32.106Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:24.824Z</t>
+    <t>2026-08-21T13:32:32.381Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:25.056Z</t>
+    <t>2026-08-21T13:32:32.620Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:25.543Z</t>
+    <t>2026-08-21T13:32:33.012Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:26.036Z</t>
+    <t>2026-08-21T13:32:33.440Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:26.884Z</t>
+    <t>2026-08-21T13:32:34.231Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:27.950Z</t>
+    <t>2026-08-21T13:32:35.154Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:29.131Z</t>
+    <t>2026-08-21T13:32:36.540Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:30.334Z</t>
+    <t>2026-08-21T13:32:37.824Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-21T12:38:30.415Z</t>
+    <t>2026-08-21T13:32:37.903Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1991</v>
+        <v>2958</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21156</v>
+        <v>21248</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>954</v>
+        <v>1077</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>1014</v>
+        <v>1227</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>966</v>
+        <v>850</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1591</v>
+        <v>1581</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>747</v>
+        <v>700</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1107</v>
+        <v>1273</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1111</v>
+        <v>1212</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>54.02 seconds</t>
+    <t>45.74 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/21/2026, 1:32:38 PM</t>
+    <t>8/27/2026, 3:18:06 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-21T13:31:54.115Z</t>
+    <t>2026-08-27T15:17:26.587Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-21T13:31:54.236Z</t>
+    <t>2026-08-27T15:17:26.707Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-21T13:31:54.348Z</t>
+    <t>2026-08-27T15:17:26.821Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:15.700Z</t>
+    <t>2026-08-27T15:17:48.073Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:15.968Z</t>
+    <t>2026-08-27T15:17:48.203Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:16.091Z</t>
+    <t>2026-08-27T15:17:48.308Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:16.217Z</t>
+    <t>2026-08-27T15:17:48.406Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:16.434Z</t>
+    <t>2026-08-27T15:17:48.608Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:16.652Z</t>
+    <t>2026-08-27T15:17:48.825Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:16.879Z</t>
+    <t>2026-08-27T15:17:49.040Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:17.102Z</t>
+    <t>2026-08-27T15:17:49.240Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:17.334Z</t>
+    <t>2026-08-27T15:17:49.455Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:18.529Z</t>
+    <t>2026-08-27T15:17:50.441Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:19.139Z</t>
+    <t>2026-08-27T15:17:51.032Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:19.797Z</t>
+    <t>2026-08-27T15:17:51.633Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:21.233Z</t>
+    <t>2026-08-27T15:17:52.246Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:21.650Z</t>
+    <t>2026-08-27T15:17:52.902Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:22.173Z</t>
+    <t>2026-08-27T15:17:53.517Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:22.399Z</t>
+    <t>2026-08-27T15:17:53.877Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:23.713Z</t>
+    <t>2026-08-27T15:17:55.304Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:23.912Z</t>
+    <t>2026-08-27T15:17:55.467Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:24.183Z</t>
+    <t>2026-08-27T15:17:55.638Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:24.508Z</t>
+    <t>2026-08-27T15:17:55.778Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:24.775Z</t>
+    <t>2026-08-27T15:17:55.917Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:24.995Z</t>
+    <t>2026-08-27T15:17:56.041Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:26.104Z</t>
+    <t>2026-08-27T15:17:56.805Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:27.272Z</t>
+    <t>2026-08-27T15:17:57.568Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:28.322Z</t>
+    <t>2026-08-27T15:17:58.256Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:30.112Z</t>
+    <t>2026-08-27T15:17:59.943Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:31.902Z</t>
+    <t>2026-08-27T15:18:01.640Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:32.106Z</t>
+    <t>2026-08-27T15:18:01.796Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:32.381Z</t>
+    <t>2026-08-27T15:18:01.964Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:32.620Z</t>
+    <t>2026-08-27T15:18:02.102Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:33.012Z</t>
+    <t>2026-08-27T15:18:02.326Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:33.440Z</t>
+    <t>2026-08-27T15:18:02.561Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:34.231Z</t>
+    <t>2026-08-27T15:18:03.220Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:35.154Z</t>
+    <t>2026-08-27T15:18:04.037Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:36.540Z</t>
+    <t>2026-08-27T15:18:05.223Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:37.824Z</t>
+    <t>2026-08-27T15:18:06.386Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-21T13:32:37.903Z</t>
+    <t>2026-08-27T15:18:06.475Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>2958</v>
+        <v>1876</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21248</v>
+        <v>21149</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>1077</v>
+        <v>889</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>1227</v>
+        <v>391</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>207</v>
+        <v>391</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>238</v>
+        <v>382</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1086</v>
+        <v>1167</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>850</v>
+        <v>651</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>931</v>
+        <v>643</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>850</v>
+        <v>568</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1581</v>
+        <v>1572</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1273</v>
+        <v>1106</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1212</v>
+        <v>1085</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>45.74 seconds</t>
+    <t>56.50 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:18:06 PM</t>
+    <t>8/27/2026, 3:18:54 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:26.587Z</t>
+    <t>2026-08-27T15:18:08.525Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:26.707Z</t>
+    <t>2026-08-27T15:18:08.687Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:26.821Z</t>
+    <t>2026-08-27T15:18:08.822Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:48.073Z</t>
+    <t>2026-08-27T15:18:30.125Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:48.203Z</t>
+    <t>2026-08-27T15:18:30.300Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:48.308Z</t>
+    <t>2026-08-27T15:18:30.425Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:48.406Z</t>
+    <t>2026-08-27T15:18:30.553Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:48.608Z</t>
+    <t>2026-08-27T15:18:30.841Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:48.825Z</t>
+    <t>2026-08-27T15:18:31.116Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:49.040Z</t>
+    <t>2026-08-27T15:18:31.386Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:49.240Z</t>
+    <t>2026-08-27T15:18:31.652Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:49.455Z</t>
+    <t>2026-08-27T15:18:31.920Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:50.441Z</t>
+    <t>2026-08-27T15:18:32.974Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:51.032Z</t>
+    <t>2026-08-27T15:18:33.799Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:51.633Z</t>
+    <t>2026-08-27T15:18:34.692Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:52.246Z</t>
+    <t>2026-08-27T15:18:35.812Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:52.902Z</t>
+    <t>2026-08-27T15:18:36.344Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:53.517Z</t>
+    <t>2026-08-27T15:18:36.931Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:53.877Z</t>
+    <t>2026-08-27T15:18:37.323Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:55.304Z</t>
+    <t>2026-08-27T15:18:38.764Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:55.467Z</t>
+    <t>2026-08-27T15:18:39.069Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:55.638Z</t>
+    <t>2026-08-27T15:18:39.456Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:55.778Z</t>
+    <t>2026-08-27T15:18:39.822Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:55.917Z</t>
+    <t>2026-08-27T15:18:40.167Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:56.041Z</t>
+    <t>2026-08-27T15:18:40.517Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:56.805Z</t>
+    <t>2026-08-27T15:18:42.011Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:57.568Z</t>
+    <t>2026-08-27T15:18:43.353Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:58.256Z</t>
+    <t>2026-08-27T15:18:44.765Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:17:59.943Z</t>
+    <t>2026-08-27T15:18:46.651Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:01.640Z</t>
+    <t>2026-08-27T15:18:48.509Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:01.796Z</t>
+    <t>2026-08-27T15:18:48.749Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:01.964Z</t>
+    <t>2026-08-27T15:18:49.098Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:02.102Z</t>
+    <t>2026-08-27T15:18:49.390Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:02.326Z</t>
+    <t>2026-08-27T15:18:49.942Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:02.561Z</t>
+    <t>2026-08-27T15:18:50.423Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:03.220Z</t>
+    <t>2026-08-27T15:18:51.219Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:04.037Z</t>
+    <t>2026-08-27T15:18:52.227Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:05.223Z</t>
+    <t>2026-08-27T15:18:53.424Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:06.386Z</t>
+    <t>2026-08-27T15:18:54.642Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:06.475Z</t>
+    <t>2026-08-27T15:18:54.750Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1876</v>
+        <v>1863</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21149</v>
+        <v>21186</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1255,7 +1255,7 @@
         <v>27</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>107</v>
+        <v>170</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>889</v>
+        <v>938</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>379</v>
+        <v>527</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>385</v>
+        <v>577</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>391</v>
+        <v>971</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>391</v>
+        <v>276</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>382</v>
+        <v>267</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1167</v>
+        <v>1111</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>651</v>
+        <v>1232</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>643</v>
+        <v>1094</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>568</v>
+        <v>1087</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1572</v>
+        <v>1596</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1566</v>
+        <v>1596</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>96</v>
+        <v>225</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>697</v>
+        <v>767</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1085</v>
+        <v>1117</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>56.50 seconds</t>
+    <t>52.49 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:18:54 PM</t>
+    <t>8/27/2026, 3:19:26 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:08.525Z</t>
+    <t>2026-08-27T15:18:38.622Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:08.687Z</t>
+    <t>2026-08-27T15:18:38.774Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:08.822Z</t>
+    <t>2026-08-27T15:18:38.920Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:30.125Z</t>
+    <t>2026-08-27T15:19:00.166Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:30.300Z</t>
+    <t>2026-08-27T15:19:00.339Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:30.425Z</t>
+    <t>2026-08-27T15:19:00.459Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:30.553Z</t>
+    <t>2026-08-27T15:19:00.597Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:30.841Z</t>
+    <t>2026-08-27T15:19:00.858Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:31.116Z</t>
+    <t>2026-08-27T15:19:01.118Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:31.386Z</t>
+    <t>2026-08-27T15:19:01.389Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:31.652Z</t>
+    <t>2026-08-27T15:19:01.652Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:31.920Z</t>
+    <t>2026-08-27T15:19:01.940Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:32.974Z</t>
+    <t>2026-08-27T15:19:03.020Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:33.799Z</t>
+    <t>2026-08-27T15:19:03.788Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:34.692Z</t>
+    <t>2026-08-27T15:19:04.576Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:35.812Z</t>
+    <t>2026-08-27T15:19:05.379Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:36.344Z</t>
+    <t>2026-08-27T15:19:06.555Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:36.931Z</t>
+    <t>2026-08-27T15:19:07.185Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:37.323Z</t>
+    <t>2026-08-27T15:19:07.598Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:38.764Z</t>
+    <t>2026-08-27T15:19:09.075Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:39.069Z</t>
+    <t>2026-08-27T15:19:09.415Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:39.456Z</t>
+    <t>2026-08-27T15:19:09.802Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:39.822Z</t>
+    <t>2026-08-27T15:19:10.216Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:40.167Z</t>
+    <t>2026-08-27T15:19:10.625Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:40.517Z</t>
+    <t>2026-08-27T15:19:10.963Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:42.011Z</t>
+    <t>2026-08-27T15:19:12.602Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:43.353Z</t>
+    <t>2026-08-27T15:19:14.192Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:44.765Z</t>
+    <t>2026-08-27T15:19:15.728Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:46.651Z</t>
+    <t>2026-08-27T15:19:17.640Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:48.509Z</t>
+    <t>2026-08-27T15:19:19.537Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:48.749Z</t>
+    <t>2026-08-27T15:19:19.880Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:49.098Z</t>
+    <t>2026-08-27T15:19:20.271Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:49.390Z</t>
+    <t>2026-08-27T15:19:20.575Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:49.942Z</t>
+    <t>2026-08-27T15:19:21.153Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:50.423Z</t>
+    <t>2026-08-27T15:19:21.649Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:51.219Z</t>
+    <t>2026-08-27T15:19:22.535Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:52.227Z</t>
+    <t>2026-08-27T15:19:23.668Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:53.424Z</t>
+    <t>2026-08-27T15:19:24.874Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:54.642Z</t>
+    <t>2026-08-27T15:19:26.063Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:54.750Z</t>
+    <t>2026-08-27T15:19:26.161Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1863</v>
+        <v>1870</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21186</v>
+        <v>21114</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1255,7 +1255,7 @@
         <v>27</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>527</v>
+        <v>486</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>577</v>
+        <v>491</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>971</v>
+        <v>544</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>276</v>
+        <v>965</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1111</v>
+        <v>1144</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>1232</v>
+        <v>1307</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1094</v>
+        <v>1234</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>1087</v>
+        <v>1229</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1596</v>
+        <v>1610</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1596</v>
+        <v>1609</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>52.49 seconds</t>
+    <t>61.69 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:19:26 PM</t>
+    <t>8/27/2026, 3:19:38 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:38.622Z</t>
+    <t>2026-08-27T15:18:54.411Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:38.774Z</t>
+    <t>2026-08-27T15:18:54.561Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:38.920Z</t>
+    <t>2026-08-27T15:18:54.733Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:00.166Z</t>
+    <t>2026-08-27T15:19:16.029Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:00.339Z</t>
+    <t>2026-08-27T15:19:16.215Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:00.459Z</t>
+    <t>2026-08-27T15:19:16.333Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:00.597Z</t>
+    <t>2026-08-27T15:19:16.448Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:00.858Z</t>
+    <t>2026-08-27T15:19:16.677Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:01.118Z</t>
+    <t>2026-08-27T15:19:16.911Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:01.389Z</t>
+    <t>2026-08-27T15:19:17.149Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:01.652Z</t>
+    <t>2026-08-27T15:19:17.371Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:01.940Z</t>
+    <t>2026-08-27T15:19:17.607Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:03.020Z</t>
+    <t>2026-08-27T15:19:18.629Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:03.788Z</t>
+    <t>2026-08-27T15:19:19.204Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:04.576Z</t>
+    <t>2026-08-27T15:19:19.821Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:05.379Z</t>
+    <t>2026-08-27T15:19:20.463Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:06.555Z</t>
+    <t>2026-08-27T15:19:21.713Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:07.185Z</t>
+    <t>2026-08-27T15:19:22.145Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:07.598Z</t>
+    <t>2026-08-27T15:19:22.374Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:09.075Z</t>
+    <t>2026-08-27T15:19:23.653Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:09.415Z</t>
+    <t>2026-08-27T15:19:23.892Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:09.802Z</t>
+    <t>2026-08-27T15:19:24.171Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:10.216Z</t>
+    <t>2026-08-27T15:19:24.502Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:10.625Z</t>
+    <t>2026-08-27T15:19:24.733Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:10.963Z</t>
+    <t>2026-08-27T15:19:24.918Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:12.602Z</t>
+    <t>2026-08-27T15:19:26.261Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:14.192Z</t>
+    <t>2026-08-27T15:19:27.566Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:15.728Z</t>
+    <t>2026-08-27T15:19:28.863Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:17.640Z</t>
+    <t>2026-08-27T15:19:30.670Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:19.537Z</t>
+    <t>2026-08-27T15:19:32.460Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:19.880Z</t>
+    <t>2026-08-27T15:19:32.796Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:20.271Z</t>
+    <t>2026-08-27T15:19:33.084Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:20.575Z</t>
+    <t>2026-08-27T15:19:33.324Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:21.153Z</t>
+    <t>2026-08-27T15:19:33.789Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:21.649Z</t>
+    <t>2026-08-27T15:19:34.221Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:22.535Z</t>
+    <t>2026-08-27T15:19:34.965Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:23.668Z</t>
+    <t>2026-08-27T15:19:35.899Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:24.874Z</t>
+    <t>2026-08-27T15:19:37.142Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:26.063Z</t>
+    <t>2026-08-27T15:19:38.304Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:26.161Z</t>
+    <t>2026-08-27T15:19:38.385Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1870</v>
+        <v>2890</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21114</v>
+        <v>21193</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1255,7 +1255,7 @@
         <v>27</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>947</v>
+        <v>900</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>486</v>
+        <v>407</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>491</v>
+        <v>401</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>544</v>
+        <v>387</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1144</v>
+        <v>1094</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>1307</v>
+        <v>1168</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1234</v>
+        <v>1145</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>1229</v>
+        <v>1101</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1610</v>
+        <v>1592</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1609</v>
+        <v>1588</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>781</v>
+        <v>718</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1123</v>
+        <v>1165</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1112</v>
+        <v>1094</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>61.69 seconds</t>
+    <t>57.73 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:19:38 PM</t>
+    <t>8/27/2026, 3:19:58 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:54.411Z</t>
+    <t>2026-08-27T15:19:11.767Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:54.561Z</t>
+    <t>2026-08-27T15:19:11.938Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:18:54.733Z</t>
+    <t>2026-08-27T15:19:12.066Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:16.029Z</t>
+    <t>2026-08-27T15:19:33.349Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:16.215Z</t>
+    <t>2026-08-27T15:19:33.540Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:16.333Z</t>
+    <t>2026-08-27T15:19:33.659Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:16.448Z</t>
+    <t>2026-08-27T15:19:33.778Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:16.677Z</t>
+    <t>2026-08-27T15:19:34.077Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:16.911Z</t>
+    <t>2026-08-27T15:19:34.364Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:17.149Z</t>
+    <t>2026-08-27T15:19:34.711Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:17.371Z</t>
+    <t>2026-08-27T15:19:35.001Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:17.607Z</t>
+    <t>2026-08-27T15:19:35.283Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:18.629Z</t>
+    <t>2026-08-27T15:19:36.351Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:19.204Z</t>
+    <t>2026-08-27T15:19:37.169Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:19.821Z</t>
+    <t>2026-08-27T15:19:37.722Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:20.463Z</t>
+    <t>2026-08-27T15:19:38.858Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:21.713Z</t>
+    <t>2026-08-27T15:19:39.353Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:22.145Z</t>
+    <t>2026-08-27T15:19:39.901Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:22.374Z</t>
+    <t>2026-08-27T15:19:40.248Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:23.653Z</t>
+    <t>2026-08-27T15:19:41.711Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:23.892Z</t>
+    <t>2026-08-27T15:19:42.190Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:24.171Z</t>
+    <t>2026-08-27T15:19:42.584Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:24.502Z</t>
+    <t>2026-08-27T15:19:43.045Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:24.733Z</t>
+    <t>2026-08-27T15:19:43.476Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:24.918Z</t>
+    <t>2026-08-27T15:19:43.785Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:26.261Z</t>
+    <t>2026-08-27T15:19:45.159Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:27.566Z</t>
+    <t>2026-08-27T15:19:46.599Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:28.863Z</t>
+    <t>2026-08-27T15:19:47.980Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:30.670Z</t>
+    <t>2026-08-27T15:19:49.889Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:32.460Z</t>
+    <t>2026-08-27T15:19:51.707Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:32.796Z</t>
+    <t>2026-08-27T15:19:52.061Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.084Z</t>
+    <t>2026-08-27T15:19:52.443Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.324Z</t>
+    <t>2026-08-27T15:19:52.762Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.789Z</t>
+    <t>2026-08-27T15:19:53.291Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:34.221Z</t>
+    <t>2026-08-27T15:19:53.876Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:34.965Z</t>
+    <t>2026-08-27T15:19:54.784Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:35.899Z</t>
+    <t>2026-08-27T15:19:55.899Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:37.142Z</t>
+    <t>2026-08-27T15:19:57.118Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:38.304Z</t>
+    <t>2026-08-27T15:19:58.344Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:38.385Z</t>
+    <t>2026-08-27T15:19:58.456Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>2890</v>
+        <v>1898</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21193</v>
+        <v>21172</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1255,7 +1255,7 @@
         <v>27</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>900</v>
+        <v>944</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>407</v>
+        <v>518</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>401</v>
+        <v>237</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>387</v>
+        <v>971</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>967</v>
+        <v>254</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>1168</v>
+        <v>1083</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1145</v>
+        <v>1094</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>1101</v>
+        <v>1072</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>718</v>
+        <v>808</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1165</v>
+        <v>1139</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1094</v>
+        <v>1132</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>57.73 seconds</t>
+    <t>51.39 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:19:58 PM</t>
+    <t>8/27/2026, 3:20:36 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:11.767Z</t>
+    <t>2026-08-27T15:19:49.538Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:11.938Z</t>
+    <t>2026-08-27T15:19:49.692Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:12.066Z</t>
+    <t>2026-08-27T15:19:49.833Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.349Z</t>
+    <t>2026-08-27T15:20:11.077Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.540Z</t>
+    <t>2026-08-27T15:20:11.268Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.659Z</t>
+    <t>2026-08-27T15:20:11.401Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:33.778Z</t>
+    <t>2026-08-27T15:20:11.538Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:34.077Z</t>
+    <t>2026-08-27T15:20:11.820Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:34.364Z</t>
+    <t>2026-08-27T15:20:12.115Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:34.711Z</t>
+    <t>2026-08-27T15:20:12.385Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:35.001Z</t>
+    <t>2026-08-27T15:20:12.668Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:35.283Z</t>
+    <t>2026-08-27T15:20:12.965Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:36.351Z</t>
+    <t>2026-08-27T15:20:14.005Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:37.169Z</t>
+    <t>2026-08-27T15:20:14.819Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:37.722Z</t>
+    <t>2026-08-27T15:20:15.358Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:38.858Z</t>
+    <t>2026-08-27T15:20:16.497Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:39.353Z</t>
+    <t>2026-08-27T15:20:17.101Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:39.901Z</t>
+    <t>2026-08-27T15:20:17.703Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:40.248Z</t>
+    <t>2026-08-27T15:20:18.035Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:41.711Z</t>
+    <t>2026-08-27T15:20:19.479Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:42.190Z</t>
+    <t>2026-08-27T15:20:19.878Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:42.584Z</t>
+    <t>2026-08-27T15:20:20.280Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:43.045Z</t>
+    <t>2026-08-27T15:20:20.686Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:43.476Z</t>
+    <t>2026-08-27T15:20:21.035Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:43.785Z</t>
+    <t>2026-08-27T15:20:21.363Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:45.159Z</t>
+    <t>2026-08-27T15:20:22.894Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:46.599Z</t>
+    <t>2026-08-27T15:20:24.368Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:47.980Z</t>
+    <t>2026-08-27T15:20:25.801Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:49.889Z</t>
+    <t>2026-08-27T15:20:27.687Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:51.707Z</t>
+    <t>2026-08-27T15:20:29.542Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:52.061Z</t>
+    <t>2026-08-27T15:20:29.910Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:52.443Z</t>
+    <t>2026-08-27T15:20:30.283Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:52.762Z</t>
+    <t>2026-08-27T15:20:30.620Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:53.291Z</t>
+    <t>2026-08-27T15:20:31.187Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:53.876Z</t>
+    <t>2026-08-27T15:20:31.777Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:54.784Z</t>
+    <t>2026-08-27T15:20:32.683Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:55.899Z</t>
+    <t>2026-08-27T15:20:33.921Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:57.118Z</t>
+    <t>2026-08-27T15:20:35.049Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:58.344Z</t>
+    <t>2026-08-27T15:20:36.327Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:58.456Z</t>
+    <t>2026-08-27T15:20:36.495Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1898</v>
+        <v>1701</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21172</v>
+        <v>21128</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1255,7 +1255,7 @@
         <v>27</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>1083</v>
+        <v>1254</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1094</v>
+        <v>1193</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>1072</v>
+        <v>1227</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1599</v>
+        <v>1595</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1593</v>
+        <v>1605</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>224</v>
+        <v>306</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>808</v>
+        <v>855</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1139</v>
+        <v>1025</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1132</v>
+        <v>1187</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>51.39 seconds</t>
+    <t>82.21 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:20:36 PM</t>
+    <t>8/27/2026, 3:21:10 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:49.538Z</t>
+    <t>2026-08-27T15:20:24.991Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:49.692Z</t>
+    <t>2026-08-27T15:20:25.281Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:19:49.833Z</t>
+    <t>2026-08-27T15:20:25.362Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:11.077Z</t>
+    <t>2026-08-27T15:20:46.802Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:11.268Z</t>
+    <t>2026-08-27T15:20:47.007Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:11.401Z</t>
+    <t>2026-08-27T15:20:47.139Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:11.538Z</t>
+    <t>2026-08-27T15:20:47.270Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:11.820Z</t>
+    <t>2026-08-27T15:20:47.529Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:12.115Z</t>
+    <t>2026-08-27T15:20:47.778Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:12.385Z</t>
+    <t>2026-08-27T15:20:48.027Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:12.668Z</t>
+    <t>2026-08-27T15:20:48.273Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:12.965Z</t>
+    <t>2026-08-27T15:20:48.529Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:14.005Z</t>
+    <t>2026-08-27T15:20:49.606Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:14.819Z</t>
+    <t>2026-08-27T15:20:50.257Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:15.358Z</t>
+    <t>2026-08-27T15:20:50.936Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:16.497Z</t>
+    <t>2026-08-27T15:20:52.208Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:17.101Z</t>
+    <t>2026-08-27T15:20:52.664Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:17.703Z</t>
+    <t>2026-08-27T15:20:53.101Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:18.035Z</t>
+    <t>2026-08-27T15:20:53.455Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:19.479Z</t>
+    <t>2026-08-27T15:20:54.859Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:19.878Z</t>
+    <t>2026-08-27T15:20:55.132Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:20.280Z</t>
+    <t>2026-08-27T15:20:55.472Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:20.686Z</t>
+    <t>2026-08-27T15:20:55.937Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:21.035Z</t>
+    <t>2026-08-27T15:20:56.287Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:21.363Z</t>
+    <t>2026-08-27T15:20:56.598Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:22.894Z</t>
+    <t>2026-08-27T15:20:57.854Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:24.368Z</t>
+    <t>2026-08-27T15:20:59.138Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:25.801Z</t>
+    <t>2026-08-27T15:21:00.236Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:27.687Z</t>
+    <t>2026-08-27T15:21:02.104Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:29.542Z</t>
+    <t>2026-08-27T15:21:03.942Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:29.910Z</t>
+    <t>2026-08-27T15:21:04.242Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:30.283Z</t>
+    <t>2026-08-27T15:21:04.543Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:30.620Z</t>
+    <t>2026-08-27T15:21:04.809Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:31.187Z</t>
+    <t>2026-08-27T15:21:05.309Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:31.777Z</t>
+    <t>2026-08-27T15:21:05.755Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:32.683Z</t>
+    <t>2026-08-27T15:21:06.524Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:33.921Z</t>
+    <t>2026-08-27T15:21:07.547Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:35.049Z</t>
+    <t>2026-08-27T15:21:09.137Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:36.327Z</t>
+    <t>2026-08-27T15:21:10.331Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:36.495Z</t>
+    <t>2026-08-27T15:21:10.433Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1701</v>
+        <v>3757</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21128</v>
+        <v>21370</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>926</v>
+        <v>964</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>522</v>
+        <v>443</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>224</v>
+        <v>452</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1108</v>
+        <v>1143</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>1254</v>
+        <v>969</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1193</v>
+        <v>1055</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>1227</v>
+        <v>920</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1595</v>
+        <v>1577</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1605</v>
+        <v>1582</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>297</v>
+        <v>201</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>306</v>
+        <v>202</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>855</v>
+        <v>783</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1025</v>
+        <v>1112</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1187</v>
+        <v>1123</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>

--- a/reports/Web/excel/selenium-report.xlsx
+++ b/reports/Web/excel/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>82.21 seconds</t>
+    <t>52.57 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 3:21:10 PM</t>
+    <t>8/27/2026, 4:40:42 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:24.991Z</t>
+    <t>2026-08-27T16:39:53.894Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:25.281Z</t>
+    <t>2026-08-27T16:39:54.050Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:25.362Z</t>
+    <t>2026-08-27T16:39:54.197Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:46.802Z</t>
+    <t>2026-08-27T16:40:15.443Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:47.007Z</t>
+    <t>2026-08-27T16:40:15.642Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:47.139Z</t>
+    <t>2026-08-27T16:40:15.791Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:47.270Z</t>
+    <t>2026-08-27T16:40:15.916Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:47.529Z</t>
+    <t>2026-08-27T16:40:16.198Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:47.778Z</t>
+    <t>2026-08-27T16:40:16.483Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:48.027Z</t>
+    <t>2026-08-27T16:40:16.767Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:48.273Z</t>
+    <t>2026-08-27T16:40:17.048Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:48.529Z</t>
+    <t>2026-08-27T16:40:17.353Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:49.606Z</t>
+    <t>2026-08-27T16:40:18.406Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:50.257Z</t>
+    <t>2026-08-27T16:40:19.295Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:50.936Z</t>
+    <t>2026-08-27T16:40:20.148Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:52.208Z</t>
+    <t>2026-08-27T16:40:21.023Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:52.664Z</t>
+    <t>2026-08-27T16:40:22.114Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:53.101Z</t>
+    <t>2026-08-27T16:40:22.792Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:53.455Z</t>
+    <t>2026-08-27T16:40:23.115Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:54.859Z</t>
+    <t>2026-08-27T16:40:24.600Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:55.132Z</t>
+    <t>2026-08-27T16:40:24.874Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:55.472Z</t>
+    <t>2026-08-27T16:40:25.217Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:55.937Z</t>
+    <t>2026-08-27T16:40:25.720Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:56.287Z</t>
+    <t>2026-08-27T16:40:26.121Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:56.598Z</t>
+    <t>2026-08-27T16:40:26.385Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:57.854Z</t>
+    <t>2026-08-27T16:40:28.127Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:20:59.138Z</t>
+    <t>2026-08-27T16:40:29.835Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:00.236Z</t>
+    <t>2026-08-27T16:40:31.634Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:02.104Z</t>
+    <t>2026-08-27T16:40:33.524Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:03.942Z</t>
+    <t>2026-08-27T16:40:35.446Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:04.242Z</t>
+    <t>2026-08-27T16:40:35.850Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:04.543Z</t>
+    <t>2026-08-27T16:40:36.312Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:04.809Z</t>
+    <t>2026-08-27T16:40:36.608Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:05.309Z</t>
+    <t>2026-08-27T16:40:37.337Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:05.755Z</t>
+    <t>2026-08-27T16:40:37.954Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:06.524Z</t>
+    <t>2026-08-27T16:40:38.844Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:07.547Z</t>
+    <t>2026-08-27T16:40:40.155Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:09.137Z</t>
+    <t>2026-08-27T16:40:41.400Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:10.331Z</t>
+    <t>2026-08-27T16:40:42.633Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T15:21:10.433Z</t>
+    <t>2026-08-27T16:40:42.723Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>3757</v>
+        <v>1798</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21370</v>
+        <v>21116</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>964</v>
+        <v>922</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>443</v>
+        <v>507</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>452</v>
+        <v>526</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>990</v>
+        <v>586</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>231</v>
+        <v>954</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>222</v>
+        <v>308</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1143</v>
+        <v>1119</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>969</v>
+        <v>1493</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1055</v>
+        <v>1474</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>920</v>
+        <v>1477</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1577</v>
+        <v>1614</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1582</v>
+        <v>1609</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>202</v>
+        <v>389</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>783</v>
+        <v>875</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1112</v>
+        <v>1157</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1123</v>
+        <v>1138</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>
